--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1504-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1504-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33C60076-274A-4CE3-BAC4-49FC1266F886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C0E896E-BEED-4503-9B83-E9E5602A91E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{144F6D4D-02B2-488E-94B4-058B6D8791CA}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{B58FD7CE-E4E2-4040-8CB9-5D66479F335B}"/>
   </bookViews>
   <sheets>
     <sheet name="1504-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1595,27 +1595,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C90851E-A35A-4F3F-B280-DA588A64D114}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B8C3E78-542C-4B19-B14F-08FE8908C4E7}">
   <dimension ref="A1:X53"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1649,7 +1648,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1685,7 +1684,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1737,7 +1736,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1805,7 +1804,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1877,7 +1876,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1949,7 +1948,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -2021,7 +2020,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2093,7 +2092,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2165,7 +2164,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2237,7 +2236,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2309,7 +2308,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2381,7 +2380,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2453,7 +2452,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2525,7 +2524,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2597,7 +2596,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2669,7 +2668,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2741,7 +2740,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2813,7 +2812,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2885,7 +2884,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2009</v>
       </c>
@@ -2957,7 +2956,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2008</v>
       </c>
@@ -3029,7 +3028,7 @@
         <v>5.55</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2007</v>
       </c>
@@ -3101,7 +3100,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2006</v>
       </c>
@@ -3173,7 +3172,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2005</v>
       </c>
@@ -3245,7 +3244,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2004</v>
       </c>
@@ -3317,7 +3316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2003</v>
       </c>
@@ -3389,7 +3388,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2002</v>
       </c>
@@ -3461,7 +3460,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2001</v>
       </c>
@@ -3533,7 +3532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2000</v>
       </c>
@@ -3605,7 +3604,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>1999</v>
       </c>
@@ -3677,7 +3676,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>1998</v>
       </c>
@@ -3749,7 +3748,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>1997</v>
       </c>
@@ -3821,7 +3820,7 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>1996</v>
       </c>
@@ -3893,7 +3892,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>1995</v>
       </c>
@@ -3965,7 +3964,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="41">
         <v>1994</v>
       </c>
@@ -4037,7 +4036,7 @@
         <v>6.65</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="43"/>
       <c r="B36" s="44"/>
       <c r="C36" s="18" t="s">
@@ -4065,7 +4064,7 @@
       <c r="W36" s="50"/>
       <c r="X36" s="46"/>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="51">
         <v>1993</v>
       </c>
@@ -4137,7 +4136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="53"/>
       <c r="B38" s="54"/>
       <c r="C38" s="20" t="s">
@@ -4165,7 +4164,7 @@
       <c r="W38" s="60"/>
       <c r="X38" s="56"/>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="41">
         <v>1992</v>
       </c>
@@ -4237,7 +4236,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="43"/>
       <c r="B40" s="44"/>
       <c r="C40" s="18" t="s">
@@ -4265,7 +4264,7 @@
       <c r="W40" s="50"/>
       <c r="X40" s="46"/>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="51">
         <v>1991</v>
       </c>
@@ -4337,7 +4336,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="53"/>
       <c r="B42" s="54"/>
       <c r="C42" s="20" t="s">
@@ -4365,7 +4364,7 @@
       <c r="W42" s="60"/>
       <c r="X42" s="56"/>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="41">
         <v>1990</v>
       </c>
@@ -4437,7 +4436,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="43"/>
       <c r="B44" s="44"/>
       <c r="C44" s="18" t="s">
@@ -4465,7 +4464,7 @@
       <c r="W44" s="50"/>
       <c r="X44" s="46"/>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="51">
         <v>1989</v>
       </c>
@@ -4537,7 +4536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="53"/>
       <c r="B46" s="54"/>
       <c r="C46" s="20" t="s">
@@ -4565,7 +4564,7 @@
       <c r="W46" s="60"/>
       <c r="X46" s="56"/>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="37">
         <v>1988</v>
       </c>
@@ -4637,7 +4636,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="39">
         <v>1987</v>
       </c>
@@ -4709,7 +4708,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="37">
         <v>1986</v>
       </c>
@@ -4781,7 +4780,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="39">
         <v>1985</v>
       </c>
@@ -4853,7 +4852,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="37">
         <v>1984</v>
       </c>
@@ -4925,7 +4924,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="39">
         <v>1983</v>
       </c>
@@ -4997,7 +4996,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="37" t="s">
         <v>67</v>
       </c>
